--- a/04_DESIGN_TABLES/DesignTable_1405_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_1405_SW2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV16"/>
+  <dimension ref="A1:AV18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1144,131 +1144,131 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1405-06-04</t>
+          <t>1405-04-06</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="C5" t="n">
-        <v>0.50807</v>
+        <v>0.39664</v>
       </c>
       <c r="D5" t="n">
-        <v>0.88</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>0.57</v>
+        <v>0.43</v>
       </c>
       <c r="F5" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="G5" t="n">
-        <v>0.57</v>
+        <v>0.43</v>
       </c>
       <c r="H5" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="I5" t="n">
         <v>0.0556</v>
       </c>
       <c r="J5" t="n">
-        <v>0.285</v>
+        <v>0.215</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3294</v>
+        <v>0.2594</v>
       </c>
       <c r="L5" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.2465</v>
+      </c>
+      <c r="N5" t="n">
         <v>0.58</v>
       </c>
-      <c r="M5" t="n">
-        <v>0.1825</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.54</v>
-      </c>
       <c r="O5" t="n">
-        <v>0.3146</v>
+        <v>0.4056</v>
       </c>
       <c r="P5" t="n">
-        <v>0.11</v>
+        <v>0.125</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.345</v>
+        <v>0.4375</v>
       </c>
       <c r="R5" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="S5" t="n">
-        <v>0.39837</v>
+        <v>0.50518</v>
       </c>
       <c r="T5" t="n">
-        <v>0.263</v>
+        <v>0.331</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2405</v>
+        <v>0.306</v>
       </c>
       <c r="V5" t="n">
         <v>0.265</v>
       </c>
       <c r="W5" t="n">
-        <v>0.263</v>
+        <v>0.331</v>
       </c>
       <c r="X5" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.4707</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.2935</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.211</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.612</v>
+      </c>
+      <c r="AD5" t="n">
         <v>0.29</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.4459</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0.1485</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0.481</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0.2875</v>
       </c>
       <c r="AE5" t="n">
         <v>0.05556</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.2405</v>
+        <v>0.306</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.28494</v>
+        <v>0.35044</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.22</v>
+        <v>0.32</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.875</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>1405-06-04</t>
+          <t>1405-04-06</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Female Pipe x Female NPSM Swivel Adapter Union, 3/8-18 NPTF (female) x 1/4-18 NPSM (female swivel)</t>
+          <t>Female Pipe x Female NPSM Swivel Adapter Union, 1/4-18 NPTF (female) x 3/8-18 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -1278,38 +1278,43 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>3/8-18 NPTF (female)</t>
+          <t>1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>1/4-18 NPSM (female swivel)</t>
+          <t>3/8-18 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>Air-Way s56 only (double-pass 17 rows) | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs), tapered helical thread over P1; W1 = port face to the nut face (overall), L1 = port face to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D from the port bottom through the stem tip</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; OMi answer 2026-10-18 (staged, not shipped): every size from OMi's drawing zip_a/1405-04-06.pdf (07_RAW_EXTRACTS/omi_answers_20261018, sha256 a5f51518eabc3b1f...; a Brennan-format sheet OMi sent in answer to our 2026-10-09 size request; user 2026-10-18: "this is verified information, use it"); one source (OMi = Brennan data, evidence 2026-09-26) -&gt; ASSUMED; tap drill / thread majors from the end library (Q-TRANSFER-ENDLIB); end and body SHAPE from the Brennan 3D files (shape only, user 2026-10-08) | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs), tapered helical thread over P1; W1 = port face to the nut face (overall), L1 = port face to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D from the port bottom through the stem tip</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | OMi answer 2026-10-18 (staged, not shipped): was MISSING (no Air-Way row / non-forged Air-Way row only); now filled from OMi's own drawing; non-forged Air-Way row NOT used | VERIFIED by user decision 2026-10-18 (A23-1: OMi's own answer counts as verified)</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1405-06-04</t>
+          <t>1405-04-06</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1405-06-06</t>
+          <t>1405-06-04</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="C6" t="n">
         <v>0.50807</v>
@@ -1339,97 +1344,97 @@
         <v>0.3294</v>
       </c>
       <c r="L6" t="n">
-        <v>0.66</v>
+        <v>0.58</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2465</v>
+        <v>0.1825</v>
       </c>
       <c r="N6" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4056</v>
+        <v>0.3146</v>
       </c>
       <c r="P6" t="n">
-        <v>0.125</v>
+        <v>0.11</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4375</v>
+        <v>0.345</v>
       </c>
       <c r="R6" t="n">
-        <v>0.32</v>
+        <v>0.28</v>
       </c>
       <c r="S6" t="n">
-        <v>0.50807</v>
+        <v>0.39837</v>
       </c>
       <c r="T6" t="n">
-        <v>0.331</v>
+        <v>0.263</v>
       </c>
       <c r="U6" t="n">
-        <v>0.306</v>
+        <v>0.2405</v>
       </c>
       <c r="V6" t="n">
         <v>0.265</v>
       </c>
       <c r="W6" t="n">
-        <v>0.331</v>
+        <v>0.263</v>
       </c>
       <c r="X6" t="n">
-        <v>0.36</v>
+        <v>0.29</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4707</v>
+        <v>0.4459</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.2935</v>
+        <v>0.225</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.211</v>
+        <v>0.1485</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.25</v>
+        <v>0.19</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.612</v>
+        <v>0.481</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.29</v>
+        <v>0.2875</v>
       </c>
       <c r="AE6" t="n">
         <v>0.05556</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.306</v>
+        <v>0.2405</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.35044</v>
+        <v>0.28494</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="AJ6" t="n">
         <v>1.33</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.88</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.32</v>
+        <v>0.28</v>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>1405-06-06</t>
+          <t>1405-06-04</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Female Pipe x Female NPSM Swivel Adapter Union, 3/8-18 NPTF (female) x 3/8-18 NPSM (female swivel)</t>
+          <t>Female Pipe x Female NPSM Swivel Adapter Union, 3/8-18 NPTF (female) x 1/4-18 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
@@ -1444,7 +1449,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>3/8-18 NPSM (female swivel)</t>
+          <t>1/4-18 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -1457,25 +1462,20 @@
           <t>Air-Way s56 only (double-pass 17 rows) | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs), tapered helical thread over P1; W1 = port face to the nut face (overall), L1 = port face to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D from the port bottom through the stem tip</t>
         </is>
       </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>Air-Way nut face to stem tip (W-L) 0.250 vs Brennan 0.220: nut placed at Air-Way W (user decision 2026-09-24)</t>
-        </is>
-      </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1405-06-06</t>
+          <t>1405-06-04</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1405-06-08</t>
+          <t>1405-06-06</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.83</v>
+        <v>1.56</v>
       </c>
       <c r="C7" t="n">
         <v>0.50807</v>
@@ -1505,97 +1505,97 @@
         <v>0.3294</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="M7" t="n">
-        <v>0.304</v>
+        <v>0.2465</v>
       </c>
       <c r="N7" t="n">
-        <v>0.72</v>
+        <v>0.58</v>
       </c>
       <c r="O7" t="n">
-        <v>0.455</v>
+        <v>0.4056</v>
       </c>
       <c r="P7" t="n">
-        <v>0.14</v>
+        <v>0.125</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.5</v>
+        <v>0.4375</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4</v>
+        <v>0.32</v>
       </c>
       <c r="S7" t="n">
-        <v>0.57735</v>
+        <v>0.50807</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4115</v>
+        <v>0.331</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3795</v>
+        <v>0.306</v>
       </c>
       <c r="V7" t="n">
-        <v>0.356</v>
+        <v>0.265</v>
       </c>
       <c r="W7" t="n">
-        <v>0.4115</v>
+        <v>0.331</v>
       </c>
       <c r="X7" t="n">
-        <v>0.4425</v>
+        <v>0.36</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.595</v>
+        <v>0.4707</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.37</v>
+        <v>0.2935</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.281</v>
+        <v>0.211</v>
       </c>
       <c r="AB7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.612</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AI7" t="n">
         <v>0.33</v>
       </c>
-      <c r="AC7" t="n">
-        <v>0.759</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0.388</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0.07142999999999999</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0.3795</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0.43664</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0.45</v>
-      </c>
       <c r="AJ7" t="n">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.02</v>
+        <v>0.9</v>
       </c>
       <c r="AL7" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.4</v>
+        <v>0.32</v>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>1405-06-08</t>
+          <t>1405-06-06</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Female Pipe x Female NPSM Swivel Adapter Union, 3/8-18 NPTF (female) x 1/2-14 NPSM (female swivel)</t>
+          <t>Female Pipe x Female NPSM Swivel Adapter Union, 3/8-18 NPTF (female) x 3/8-18 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>1/2-14 NPSM (female swivel)</t>
+          <t>3/8-18 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -1625,143 +1625,143 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>Air-Way nut face to stem tip (W-L) 0.330 vs Brennan 0.280: nut placed at Air-Way W (user decision 2026-09-24)</t>
+          <t>Air-Way nut face to stem tip (W-L) 0.250 vs Brennan 0.220: nut placed at Air-Way W (user decision 2026-09-24)</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1405-06-08</t>
+          <t>1405-06-06</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1405-08-06</t>
+          <t>1405-06-08</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="C8" t="n">
+        <v>0.50807</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.0556</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.3294</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S8" t="n">
         <v>0.57735</v>
       </c>
-      <c r="D8" t="n">
+      <c r="T8" t="n">
+        <v>0.4115</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.3795</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.4115</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.4425</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.759</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.3795</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.43664</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AL8" t="n">
         <v>1</v>
       </c>
-      <c r="E8" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.07140000000000001</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.4071</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.2465</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.4056</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.4375</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.50807</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.331</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0.306</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0.331</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0.4707</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0.2935</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0.211</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0.612</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0.05556</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0.306</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0.35044</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0.88</v>
-      </c>
       <c r="AM8" t="n">
-        <v>0.32</v>
+        <v>0.4</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>1405-08-06</t>
+          <t>1405-06-08</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Female Pipe x Female NPSM Swivel Adapter Union, 1/2-14 NPTF (female) x 3/8-18 NPSM (female swivel)</t>
+          <t>Female Pipe x Female NPSM Swivel Adapter Union, 3/8-18 NPTF (female) x 1/2-14 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>1/2-14 NPTF (female)</t>
+          <t>3/8-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>3/8-18 NPSM (female swivel)</t>
+          <t>1/2-14 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -1791,143 +1791,143 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>Air-Way nut face to stem tip (W-L) 0.250 vs Brennan 0.220: nut placed at Air-Way W (user decision 2026-09-24)</t>
+          <t>Air-Way nut face to stem tip (W-L) 0.330 vs Brennan 0.280: nut placed at Air-Way W (user decision 2026-09-24)</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1405-08-06</t>
+          <t>1405-06-08</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1405-12-08</t>
+          <t>1405-08-06</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7216900000000001</v>
+        <v>0.57735</v>
       </c>
       <c r="D9" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>0.91</v>
+        <v>0.7</v>
       </c>
       <c r="F9" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="G9" t="n">
-        <v>0.91</v>
+        <v>0.7</v>
       </c>
       <c r="H9" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="I9" t="n">
         <v>0.07140000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>0.455</v>
+        <v>0.35</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5121</v>
+        <v>0.4071</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="M9" t="n">
-        <v>0.304</v>
+        <v>0.2465</v>
       </c>
       <c r="N9" t="n">
-        <v>0.72</v>
+        <v>0.58</v>
       </c>
       <c r="O9" t="n">
-        <v>0.455</v>
+        <v>0.4056</v>
       </c>
       <c r="P9" t="n">
-        <v>0.14</v>
+        <v>0.125</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.5</v>
+        <v>0.4375</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4</v>
+        <v>0.32</v>
       </c>
       <c r="S9" t="n">
-        <v>0.57735</v>
+        <v>0.50807</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4115</v>
+        <v>0.331</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3795</v>
+        <v>0.306</v>
       </c>
       <c r="V9" t="n">
-        <v>0.356</v>
+        <v>0.265</v>
       </c>
       <c r="W9" t="n">
-        <v>0.4115</v>
+        <v>0.331</v>
       </c>
       <c r="X9" t="n">
-        <v>0.4425</v>
+        <v>0.36</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.595</v>
+        <v>0.4707</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.37</v>
+        <v>0.2935</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.281</v>
+        <v>0.211</v>
       </c>
       <c r="AB9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.612</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI9" t="n">
         <v>0.33</v>
       </c>
-      <c r="AC9" t="n">
-        <v>0.759</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0.388</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0.07142999999999999</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0.3795</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0.43664</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0.45</v>
-      </c>
       <c r="AJ9" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AL9" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.4</v>
+        <v>0.32</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>1405-12-08</t>
+          <t>1405-08-06</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Female Pipe x Female NPSM Swivel Adapter Union, 3/4-14 NPTF (female) x 1/2-14 NPSM (female swivel)</t>
+          <t>Female Pipe x Female NPSM Swivel Adapter Union, 1/2-14 NPTF (female) x 3/8-18 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>3/4-14 NPTF (female)</t>
+          <t>1/2-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>1/2-14 NPSM (female swivel)</t>
+          <t>3/8-18 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -1957,23 +1957,23 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>Air-Way nut face to stem tip (W-L) 0.330 vs Brennan 0.280: nut placed at Air-Way W (user decision 2026-09-24)</t>
+          <t>Air-Way nut face to stem tip (W-L) 0.250 vs Brennan 0.220: nut placed at Air-Way W (user decision 2026-09-24)</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1405-12-08</t>
+          <t>1405-08-06</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1405-12-12</t>
+          <t>1405-08-12</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="C10" t="n">
         <v>0.7216900000000001</v>
@@ -1982,28 +1982,28 @@
         <v>1.25</v>
       </c>
       <c r="E10" t="n">
-        <v>0.91</v>
+        <v>0.7</v>
       </c>
       <c r="F10" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="G10" t="n">
-        <v>0.91</v>
+        <v>0.7</v>
       </c>
       <c r="H10" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="I10" t="n">
         <v>0.07140000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>0.455</v>
+        <v>0.35</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5121</v>
+        <v>0.4071</v>
       </c>
       <c r="L10" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="M10" t="n">
         <v>0.389</v>
@@ -2051,7 +2051,7 @@
         <v>0.375</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="AC10" t="n">
         <v>0.97</v>
@@ -2069,16 +2069,16 @@
         <v>0.54214</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AL10" t="n">
         <v>1.25</v>
@@ -2088,12 +2088,12 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>1405-12-12</t>
+          <t>1405-08-12</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Female Pipe x Female NPSM Swivel Adapter Union, 3/4-14 NPTF (female) x 3/4-14 NPSM (female swivel)</t>
+          <t>Female Pipe x Female NPSM Swivel Adapter Union, 1/2-14 NPTF (female) x 3/4-14 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>3/4-14 NPTF (female)</t>
+          <t>1/2-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -2113,28 +2113,33 @@
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>Air-Way s56 only (double-pass 17 rows) | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs), tapered helical thread over P1; W1 = port face to the nut face (overall), L1 = port face to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D from the port bottom through the stem tip</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; OMi answer 2026-10-18 (staged, not shipped): every size from OMi's drawing zip_a/1405-08-12.pdf (07_RAW_EXTRACTS/omi_answers_20261018, sha256 3bfe55d41c442cdb...; a Brennan-format sheet OMi sent in answer to our 2026-10-09 size request; user 2026-10-18: "this is verified information, use it"); one source (OMi = Brennan data, evidence 2026-09-26) -&gt; ASSUMED; tap drill / thread majors from the end library (Q-TRANSFER-ENDLIB); end and body SHAPE from the Brennan 3D files (shape only, user 2026-10-08) | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs), tapered helical thread over P1; W1 = port face to the nut face (overall), L1 = port face to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D from the port bottom through the stem tip</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | OMi answer 2026-10-18 (staged, not shipped): was MISSING (no Air-Way row / non-forged Air-Way row only); now filled from OMi's own drawing; non-forged Air-Way row NOT used | VERIFIED by user decision 2026-10-18 (A23-1: OMi's own answer counts as verified)</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1405-12-12</t>
+          <t>1405-08-12</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1405-12-16</t>
+          <t>1405-12-08</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="C11" t="n">
         <v>0.7216900000000001</v>
@@ -2164,97 +2169,97 @@
         <v>0.5121</v>
       </c>
       <c r="L11" t="n">
-        <v>0.97</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>0.525</v>
+        <v>0.304</v>
       </c>
       <c r="N11" t="n">
-        <v>0.9</v>
+        <v>0.72</v>
       </c>
       <c r="O11" t="n">
-        <v>0.7098</v>
+        <v>0.455</v>
       </c>
       <c r="P11" t="n">
-        <v>0.175</v>
+        <v>0.14</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="S11" t="n">
-        <v>0.86603</v>
+        <v>0.57735</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6465</v>
+        <v>0.4115</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6055</v>
+        <v>0.3795</v>
       </c>
       <c r="V11" t="n">
-        <v>0.428</v>
+        <v>0.356</v>
       </c>
       <c r="W11" t="n">
-        <v>0.6465</v>
+        <v>0.4115</v>
       </c>
       <c r="X11" t="n">
-        <v>0.67</v>
+        <v>0.4425</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.7447</v>
+        <v>0.595</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.59</v>
+        <v>0.37</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.4845</v>
+        <v>0.281</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.211</v>
+        <v>0.759</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.469</v>
+        <v>0.388</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.08696</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.6055</v>
+        <v>0.3795</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.6750699999999999</v>
+        <v>0.43664</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.84</v>
+        <v>0.45</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.94</v>
+        <v>1.52</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.33</v>
+        <v>1.02</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>1405-12-16</t>
+          <t>1405-12-08</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Female Pipe x Female NPSM Swivel Adapter Union, 3/4-14 NPTF (female) x 1-11 1/2 NPSM (female swivel)</t>
+          <t>Female Pipe x Female NPSM Swivel Adapter Union, 3/4-14 NPTF (female) x 1/2-14 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
@@ -2269,7 +2274,7 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1-11 1/2 NPSM (female swivel)</t>
+          <t>1/2-14 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -2284,50 +2289,50 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>Air-Way nut face to stem tip (W-L) 0.380 vs Brennan 0.350: nut placed at Air-Way W (user decision 2026-09-24)</t>
+          <t>Air-Way nut face to stem tip (W-L) 0.330 vs Brennan 0.280: nut placed at Air-Way W (user decision 2026-09-24)</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1405-12-16</t>
+          <t>1405-12-08</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1405-16-12</t>
+          <t>1405-12-12</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.23</v>
+        <v>1.96</v>
       </c>
       <c r="C12" t="n">
-        <v>0.86603</v>
+        <v>0.7216900000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="E12" t="n">
-        <v>1.14</v>
+        <v>0.91</v>
       </c>
       <c r="F12" t="n">
-        <v>1.14</v>
+        <v>0.91</v>
       </c>
       <c r="G12" t="n">
-        <v>1.14</v>
+        <v>0.91</v>
       </c>
       <c r="H12" t="n">
-        <v>1.14</v>
+        <v>0.91</v>
       </c>
       <c r="I12" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>0.57</v>
+        <v>0.455</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6395999999999999</v>
+        <v>0.5121</v>
       </c>
       <c r="L12" t="n">
         <v>0.78</v>
@@ -2396,16 +2401,16 @@
         <v>0.54214</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.23</v>
+        <v>1.96</v>
       </c>
       <c r="AI12" t="n">
         <v>0.63</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.92</v>
+        <v>1.65</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.45</v>
+        <v>1.18</v>
       </c>
       <c r="AL12" t="n">
         <v>1.25</v>
@@ -2415,12 +2420,12 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>1405-16-12</t>
+          <t>1405-12-12</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Female Pipe x Female NPSM Swivel Adapter Union, 1-11 1/2 NPTF (female) x 3/4-14 NPSM (female swivel)</t>
+          <t>Female Pipe x Female NPSM Swivel Adapter Union, 3/4-14 NPTF (female) x 3/4-14 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
@@ -2430,7 +2435,7 @@
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>1-11 1/2 NPTF (female)</t>
+          <t>3/4-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -2450,45 +2455,45 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1405-16-12</t>
+          <t>1405-12-12</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1405-16-16</t>
+          <t>1405-12-16</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2.3</v>
       </c>
       <c r="C13" t="n">
-        <v>0.86603</v>
+        <v>0.7216900000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="E13" t="n">
-        <v>1.14</v>
+        <v>0.91</v>
       </c>
       <c r="F13" t="n">
-        <v>1.14</v>
+        <v>0.91</v>
       </c>
       <c r="G13" t="n">
-        <v>1.14</v>
+        <v>0.91</v>
       </c>
       <c r="H13" t="n">
-        <v>1.14</v>
+        <v>0.91</v>
       </c>
       <c r="I13" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>0.57</v>
+        <v>0.455</v>
       </c>
       <c r="K13" t="n">
-        <v>0.6395999999999999</v>
+        <v>0.5121</v>
       </c>
       <c r="L13" t="n">
         <v>0.97</v>
@@ -2576,12 +2581,12 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>1405-16-16</t>
+          <t>1405-12-16</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Female Pipe x Female NPSM Swivel Adapter Union, 1-11 1/2 NPTF (female) x 1-11 1/2 NPSM (female swivel)</t>
+          <t>Female Pipe x Female NPSM Swivel Adapter Union, 3/4-14 NPTF (female) x 1-11 1/2 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
@@ -2591,7 +2596,7 @@
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>1-11 1/2 NPTF (female)</t>
+          <t>3/4-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
@@ -2616,138 +2621,138 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1405-16-16</t>
+          <t>1405-12-16</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1405-20-20</t>
+          <t>1405-16-12</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.43</v>
+        <v>2.23</v>
       </c>
       <c r="C14" t="n">
-        <v>1.08542</v>
+        <v>0.86603</v>
       </c>
       <c r="D14" t="n">
-        <v>1.88</v>
+        <v>1.5</v>
       </c>
       <c r="E14" t="n">
-        <v>1.48</v>
+        <v>1.14</v>
       </c>
       <c r="F14" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="G14" t="n">
-        <v>1.48</v>
+        <v>1.14</v>
       </c>
       <c r="H14" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="I14" t="n">
         <v>0.08699999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>0.74</v>
+        <v>0.57</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8096</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>1.05</v>
+        <v>0.78</v>
       </c>
       <c r="M14" t="n">
-        <v>0.695</v>
+        <v>0.389</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>0.745</v>
       </c>
       <c r="O14" t="n">
-        <v>0.9048</v>
+        <v>0.5694</v>
       </c>
       <c r="P14" t="n">
-        <v>0.195</v>
+        <v>0.135</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.9375</v>
+        <v>0.625</v>
       </c>
       <c r="R14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="S14" t="n">
-        <v>1.08542</v>
+        <v>0.7216900000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>0.819</v>
+        <v>0.517</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7775</v>
+        <v>0.485</v>
       </c>
       <c r="V14" t="n">
-        <v>0.497</v>
+        <v>0.361</v>
       </c>
       <c r="W14" t="n">
-        <v>0.819</v>
+        <v>0.517</v>
       </c>
       <c r="X14" t="n">
-        <v>0.85</v>
+        <v>0.5625</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.8141</v>
+        <v>0.6189</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.768</v>
+        <v>0.4635</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.6405</v>
+        <v>0.375</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.43</v>
+        <v>0.33</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.555</v>
+        <v>0.97</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.5385</v>
+        <v>0.393</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.08696</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.7775</v>
+        <v>0.485</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.84707</v>
+        <v>0.54214</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.43</v>
+        <v>2.23</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.01</v>
+        <v>0.63</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.88</v>
+        <v>1.25</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>1405-20-20</t>
+          <t>1405-16-12</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Female Pipe x Female NPSM Swivel Adapter Union, 1 1/4-11 1/2 NPTF (female) x 1 1/4-11 1/2 NPSM (female swivel)</t>
+          <t>Female Pipe x Female NPSM Swivel Adapter Union, 1-11 1/2 NPTF (female) x 3/4-14 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
@@ -2757,12 +2762,12 @@
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>1 1/4-11 1/2 NPTF (female)</t>
+          <t>1-11 1/2 NPTF (female)</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>1 1/4-11 1/2 NPSM (female swivel)</t>
+          <t>3/4-14 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -2777,138 +2782,138 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1405-20-20</t>
+          <t>1405-16-12</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1405-24-24</t>
+          <t>1405-16-16</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="C15" t="n">
-        <v>1.22976</v>
+        <v>0.86603</v>
       </c>
       <c r="D15" t="n">
-        <v>2.13</v>
+        <v>1.5</v>
       </c>
       <c r="E15" t="n">
-        <v>1.72</v>
+        <v>1.14</v>
       </c>
       <c r="F15" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="G15" t="n">
-        <v>1.72</v>
+        <v>1.14</v>
       </c>
       <c r="H15" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="I15" t="n">
         <v>0.08699999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>0.86</v>
+        <v>0.57</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9296</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>1.165</v>
+        <v>0.97</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8075</v>
+        <v>0.525</v>
       </c>
       <c r="N15" t="n">
-        <v>1.125</v>
+        <v>0.9</v>
       </c>
       <c r="O15" t="n">
-        <v>1.027</v>
+        <v>0.7098</v>
       </c>
       <c r="P15" t="n">
-        <v>0.195</v>
+        <v>0.175</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.0625</v>
+        <v>0.75</v>
       </c>
       <c r="R15" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="S15" t="n">
-        <v>1.22976</v>
+        <v>0.86603</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9385</v>
+        <v>0.6465</v>
       </c>
       <c r="U15" t="n">
-        <v>0.897</v>
+        <v>0.6055</v>
       </c>
       <c r="V15" t="n">
-        <v>0.503</v>
+        <v>0.428</v>
       </c>
       <c r="W15" t="n">
-        <v>0.9385</v>
+        <v>0.6465</v>
       </c>
       <c r="X15" t="n">
-        <v>0.9675</v>
+        <v>0.67</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.9392</v>
+        <v>0.7447</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.879</v>
+        <v>0.59</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.75</v>
+        <v>0.4845</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.794</v>
+        <v>1.211</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.5445</v>
+        <v>0.469</v>
       </c>
       <c r="AE15" t="n">
         <v>0.08696</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.897</v>
+        <v>0.6055</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.96657</v>
+        <v>0.6750699999999999</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.26</v>
+        <v>0.84</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.255</v>
+        <v>1.33</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.13</v>
+        <v>1.5</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>1405-24-24</t>
+          <t>1405-16-16</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Female Pipe x Female NPSM Swivel Adapter Union, 1 1/2-11 1/2 NPTF (female) x 1 1/2-11 1/2 NPSM (female swivel)</t>
+          <t>Female Pipe x Female NPSM Swivel Adapter Union, 1-11 1/2 NPTF (female) x 1-11 1/2 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
@@ -2918,12 +2923,12 @@
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>1 1/2-11 1/2 NPTF (female)</t>
+          <t>1-11 1/2 NPTF (female)</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>1 1/2-11 1/2 NPSM (female swivel)</t>
+          <t>1-11 1/2 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -2936,168 +2941,495 @@
           <t>Air-Way s56 only (double-pass 17 rows) | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs), tapered helical thread over P1; W1 = port face to the nut face (overall), L1 = port face to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D from the port bottom through the stem tip</t>
         </is>
       </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>Air-Way nut face to stem tip (W-L) 0.380 vs Brennan 0.350: nut placed at Air-Way W (user decision 2026-09-24)</t>
+        </is>
+      </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1405-24-24</t>
+          <t>1405-16-16</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1405-32-32</t>
+          <t>1405-20-20</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="C16" t="n">
-        <v>1.51843</v>
+        <v>1.08542</v>
       </c>
       <c r="D16" t="n">
-        <v>2.63</v>
+        <v>1.88</v>
       </c>
       <c r="E16" t="n">
-        <v>2.19</v>
+        <v>1.48</v>
       </c>
       <c r="F16" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="G16" t="n">
-        <v>2.19</v>
+        <v>1.48</v>
       </c>
       <c r="H16" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="I16" t="n">
         <v>0.08699999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>1.095</v>
+        <v>0.74</v>
       </c>
       <c r="K16" t="n">
-        <v>1.1646</v>
+        <v>0.8096</v>
       </c>
       <c r="L16" t="n">
-        <v>1.155</v>
+        <v>1.05</v>
       </c>
       <c r="M16" t="n">
-        <v>1.0215</v>
+        <v>0.695</v>
       </c>
       <c r="N16" t="n">
-        <v>1.125</v>
+        <v>1</v>
       </c>
       <c r="O16" t="n">
-        <v>1.2766</v>
+        <v>0.9048</v>
       </c>
       <c r="P16" t="n">
         <v>0.195</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.31</v>
+        <v>0.9375</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="S16" t="n">
-        <v>1.51843</v>
+        <v>1.08542</v>
       </c>
       <c r="T16" t="n">
-        <v>1.1755</v>
+        <v>0.819</v>
       </c>
       <c r="U16" t="n">
-        <v>1.134</v>
+        <v>0.7775</v>
       </c>
       <c r="V16" t="n">
-        <v>0.502</v>
+        <v>0.497</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1755</v>
+        <v>0.819</v>
       </c>
       <c r="X16" t="n">
-        <v>1.2125</v>
+        <v>0.85</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.9385</v>
+        <v>0.8141</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.0985</v>
+        <v>0.768</v>
       </c>
       <c r="AA16" t="n">
-        <v>1</v>
+        <v>0.6405</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.268</v>
+        <v>1.555</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.5435</v>
+        <v>0.5385</v>
       </c>
       <c r="AE16" t="n">
         <v>0.08696</v>
       </c>
       <c r="AF16" t="n">
+        <v>0.7775</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0.84707</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>1405-20-20</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Female Pipe x Female NPSM Swivel Adapter Union, 1 1/4-11 1/2 NPTF (female) x 1 1/4-11 1/2 NPSM (female swivel)</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 NPSM (female swivel)</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>Air-Way s56 only (double-pass 17 rows) | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs), tapered helical thread over P1; W1 = port face to the nut face (overall), L1 = port face to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D from the port bottom through the stem tip</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>1405-20-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1405-24-24</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1.22976</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.9296</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.165</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.8075</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.027</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.22976</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.9385</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.503</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.9385</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.9675</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.9392</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.794</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.5445</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0.96657</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.255</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>1405-24-24</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Female Pipe x Female NPSM Swivel Adapter Union, 1 1/2-11 1/2 NPTF (female) x 1 1/2-11 1/2 NPSM (female swivel)</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>1 1/2-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>1 1/2-11 1/2 NPSM (female swivel)</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>Air-Way s56 only (double-pass 17 rows) | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs), tapered helical thread over P1; W1 = port face to the nut face (overall), L1 = port face to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D from the port bottom through the stem tip</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>1405-24-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1405-32-32</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1.51843</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.095</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.1646</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.155</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.0215</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.2766</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.51843</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.1755</v>
+      </c>
+      <c r="U18" t="n">
         <v>1.134</v>
       </c>
-      <c r="AG16" t="n">
+      <c r="V18" t="n">
+        <v>0.502</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.1755</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.2125</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.9385</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.0985</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.268</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.5435</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.134</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.20357</v>
       </c>
-      <c r="AH16" t="n">
+      <c r="AH18" t="n">
         <v>2.54</v>
       </c>
-      <c r="AI16" t="n">
+      <c r="AI18" t="n">
         <v>1.72</v>
       </c>
-      <c r="AJ16" t="n">
+      <c r="AJ18" t="n">
         <v>2.15</v>
       </c>
-      <c r="AK16" t="n">
+      <c r="AK18" t="n">
         <v>1.385</v>
       </c>
-      <c r="AL16" t="n">
+      <c r="AL18" t="n">
         <v>2.63</v>
       </c>
-      <c r="AM16" t="n">
+      <c r="AM18" t="n">
         <v>0.5629999999999999</v>
       </c>
-      <c r="AN16" t="inlineStr">
+      <c r="AN18" t="inlineStr">
         <is>
           <t>1405-32-32</t>
         </is>
       </c>
-      <c r="AO16" t="inlineStr">
+      <c r="AO18" t="inlineStr">
         <is>
           <t>Female Pipe x Female NPSM Swivel Adapter Union, 2-11 1/2 NPTF (female) x 2-11 1/2 NPSM (female swivel)</t>
         </is>
       </c>
-      <c r="AP16" t="inlineStr">
+      <c r="AP18" t="inlineStr">
         <is>
           <t>1405</t>
         </is>
       </c>
-      <c r="AQ16" t="inlineStr">
+      <c r="AQ18" t="inlineStr">
         <is>
           <t>2-11 1/2 NPTF (female)</t>
         </is>
       </c>
-      <c r="AR16" t="inlineStr">
+      <c r="AR18" t="inlineStr">
         <is>
           <t>2-11 1/2 NPSM (female swivel)</t>
         </is>
       </c>
-      <c r="AS16" t="inlineStr">
+      <c r="AS18" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="AT16" t="inlineStr">
+      <c r="AT18" t="inlineStr">
         <is>
           <t>Air-Way s56 only (double-pass 17 rows) | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs), tapered helical thread over P1; W1 = port face to the nut face (overall), L1 = port face to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D from the port bottom through the stem tip</t>
         </is>
       </c>
-      <c r="AV16" t="inlineStr">
+      <c r="AV18" t="inlineStr">
         <is>
           <t>1405-32-32</t>
         </is>
